--- a/hierarchy.xlsx
+++ b/hierarchy.xlsx
@@ -5,20 +5,31 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radwan.mohamed\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radwan.mohamed\Downloads\Main Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256AC54A-8939-453A-AA21-C803B60C78AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7CD2D2-E182-431A-8EB3-D0D09AC4896A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-900" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" r:id="rId1"/>
     <sheet name="Hierarchy" sheetId="2" r:id="rId2"/>
     <sheet name="Validation" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -27,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="443">
   <si>
     <t>Hierarchy – Final Portal Preparation</t>
   </si>
@@ -383,12 +394,6 @@
     <t>Gharbya</t>
   </si>
   <si>
-    <t>30021373</t>
-  </si>
-  <si>
-    <t>Omar Ashraf Abdelfattah Atya</t>
-  </si>
-  <si>
     <t>Lead, FinTech</t>
   </si>
   <si>
@@ -740,12 +745,6 @@
     <t>Madonna Maher Yacoub Abdel Qoudous</t>
   </si>
   <si>
-    <t>30022131</t>
-  </si>
-  <si>
-    <t>Ereny Tharwat Halem Amin</t>
-  </si>
-  <si>
     <t>30022138</t>
   </si>
   <si>
@@ -824,12 +823,6 @@
     <t>Osama Fathy Naseef Bekhet</t>
   </si>
   <si>
-    <t>30021094</t>
-  </si>
-  <si>
-    <t>Moaaz Ahmed Hussien Hamza</t>
-  </si>
-  <si>
     <t>30021977</t>
   </si>
   <si>
@@ -1022,12 +1015,6 @@
     <t>Kafr Shikh</t>
   </si>
   <si>
-    <t>30021372</t>
-  </si>
-  <si>
-    <t>Omnia Mohamed Helmy Mohamed</t>
-  </si>
-  <si>
     <t>30021949</t>
   </si>
   <si>
@@ -1079,12 +1066,6 @@
     <t>Amr yehia Abdelmonem Mohamed</t>
   </si>
   <si>
-    <t>30020793</t>
-  </si>
-  <si>
-    <t>Mohamed Hassan Gendy Hassan Saed</t>
-  </si>
-  <si>
     <t>30021329</t>
   </si>
   <si>
@@ -1365,6 +1346,27 @@
   </si>
   <si>
     <t>Current Access Level</t>
+  </si>
+  <si>
+    <t>30022101</t>
+  </si>
+  <si>
+    <t>30022399</t>
+  </si>
+  <si>
+    <t>30022404</t>
+  </si>
+  <si>
+    <t>Yousef Adel Abdelhamid Mohamed</t>
+  </si>
+  <si>
+    <t>Ahmed Mohamed Elsayed Mahmoud Elsayed Mashaly</t>
+  </si>
+  <si>
+    <t>Mahmoud Mohamed Mahmoud Ismail Mohamed</t>
+  </si>
+  <si>
+    <t>Daqhlia, Dumiatte, Port-said</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1480,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF166534"/>
@@ -1520,7 +1542,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="HierarchyFinal" displayName="HierarchyFinal" ref="A1:L173" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="HierarchyFinal" displayName="HierarchyFinal" ref="A1:L171" totalsRowShown="0">
+  <autoFilter ref="A1:L171" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Functional Code"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Employee Name"/>
@@ -1864,13 +1887,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -2996,13 +3020,13 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>27</v>
@@ -3017,14 +3041,14 @@
         <v>112</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>32</v>
@@ -3033,13 +3057,13 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>27</v>
@@ -3054,14 +3078,14 @@
         <v>112</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>32</v>
@@ -3076,7 +3100,7 @@
         <v>128</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>27</v>
@@ -3091,14 +3115,14 @@
         <v>112</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>32</v>
@@ -3113,7 +3137,7 @@
         <v>130</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>27</v>
@@ -3128,21 +3152,21 @@
         <v>112</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M34" s="8"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" ht="27.6">
       <c r="A35" s="1" t="s">
         <v>131</v>
       </c>
@@ -3150,7 +3174,7 @@
         <v>132</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>27</v>
@@ -3165,95 +3189,95 @@
         <v>112</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M35" s="8"/>
     </row>
-    <row r="36" spans="1:13" ht="27.6">
+    <row r="36" spans="1:13">
       <c r="A36" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M36" s="8"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M37" s="8"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" ht="27.6">
       <c r="A38" s="1" t="s">
         <v>139</v>
       </c>
@@ -3261,36 +3285,36 @@
         <v>140</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M38" s="8"/>
     </row>
-    <row r="39" spans="1:13" ht="27.6">
+    <row r="39" spans="1:13">
       <c r="A39" s="1" t="s">
         <v>141</v>
       </c>
@@ -3298,36 +3322,36 @@
         <v>142</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M39" s="8"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" ht="27.6">
       <c r="A40" s="1" t="s">
         <v>143</v>
       </c>
@@ -3335,36 +3359,36 @@
         <v>144</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M40" s="8"/>
     </row>
-    <row r="41" spans="1:13" ht="27.6">
+    <row r="41" spans="1:13">
       <c r="A41" s="1" t="s">
         <v>145</v>
       </c>
@@ -3372,32 +3396,32 @@
         <v>146</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M41" s="8"/>
     </row>
@@ -3409,29 +3433,29 @@
         <v>148</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>32</v>
@@ -3446,29 +3470,29 @@
         <v>150</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>32</v>
@@ -3483,29 +3507,29 @@
         <v>152</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>32</v>
@@ -3520,7 +3544,7 @@
         <v>154</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>101</v>
@@ -3535,14 +3559,14 @@
         <v>98</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>32</v>
@@ -3557,7 +3581,7 @@
         <v>156</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>101</v>
@@ -3572,14 +3596,14 @@
         <v>98</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>32</v>
@@ -3594,7 +3618,7 @@
         <v>158</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>101</v>
@@ -3609,21 +3633,21 @@
         <v>98</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M47" s="8"/>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" ht="27.6">
       <c r="A48" s="1" t="s">
         <v>159</v>
       </c>
@@ -3631,7 +3655,7 @@
         <v>160</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>101</v>
@@ -3646,17 +3670,17 @@
         <v>98</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M48" s="8"/>
     </row>
@@ -3683,21 +3707,21 @@
         <v>98</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
         <v>31</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M49" s="8"/>
     </row>
-    <row r="50" spans="1:13" ht="27.6">
+    <row r="50" spans="1:13">
       <c r="A50" s="1" t="s">
         <v>163</v>
       </c>
@@ -3705,36 +3729,36 @@
         <v>164</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M50" s="8"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" ht="27.6">
       <c r="A51" s="1" t="s">
         <v>165</v>
       </c>
@@ -3742,7 +3766,7 @@
         <v>166</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>117</v>
@@ -3757,17 +3781,17 @@
         <v>115</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M51" s="8"/>
     </row>
@@ -3779,7 +3803,7 @@
         <v>168</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>117</v>
@@ -3794,17 +3818,17 @@
         <v>115</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M52" s="8"/>
     </row>
@@ -3816,7 +3840,7 @@
         <v>170</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>117</v>
@@ -3831,21 +3855,21 @@
         <v>115</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M53" s="8"/>
     </row>
-    <row r="54" spans="1:13" ht="27.6">
+    <row r="54" spans="1:13">
       <c r="A54" s="1" t="s">
         <v>171</v>
       </c>
@@ -3853,36 +3877,36 @@
         <v>172</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M54" s="8"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" ht="27.6">
       <c r="A55" s="1" t="s">
         <v>173</v>
       </c>
@@ -3890,7 +3914,7 @@
         <v>174</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>105</v>
@@ -3905,21 +3929,21 @@
         <v>103</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M55" s="8"/>
     </row>
-    <row r="56" spans="1:13" ht="27.6">
+    <row r="56" spans="1:13">
       <c r="A56" s="1" t="s">
         <v>175</v>
       </c>
@@ -3927,7 +3951,7 @@
         <v>176</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>105</v>
@@ -3942,14 +3966,14 @@
         <v>103</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>32</v>
@@ -3964,7 +3988,7 @@
         <v>178</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>105</v>
@@ -3979,21 +4003,21 @@
         <v>103</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M57" s="8"/>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" ht="27.6">
       <c r="A58" s="1" t="s">
         <v>179</v>
       </c>
@@ -4001,7 +4025,7 @@
         <v>180</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>105</v>
@@ -4016,21 +4040,21 @@
         <v>103</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M58" s="8"/>
     </row>
-    <row r="59" spans="1:13" ht="27.6">
+    <row r="59" spans="1:13">
       <c r="A59" s="1" t="s">
         <v>181</v>
       </c>
@@ -4038,32 +4062,32 @@
         <v>182</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M59" s="8"/>
     </row>
@@ -4075,7 +4099,7 @@
         <v>184</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>108</v>
@@ -4090,14 +4114,14 @@
         <v>106</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>32</v>
@@ -4112,7 +4136,7 @@
         <v>186</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>108</v>
@@ -4127,14 +4151,14 @@
         <v>106</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>32</v>
@@ -4149,7 +4173,7 @@
         <v>188</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>108</v>
@@ -4164,21 +4188,21 @@
         <v>106</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M62" s="8"/>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" ht="27.6">
       <c r="A63" s="1" t="s">
         <v>189</v>
       </c>
@@ -4186,7 +4210,7 @@
         <v>190</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>108</v>
@@ -4201,21 +4225,21 @@
         <v>106</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M63" s="8"/>
     </row>
-    <row r="64" spans="1:13" ht="27.6">
+    <row r="64" spans="1:13">
       <c r="A64" s="1" t="s">
         <v>191</v>
       </c>
@@ -4223,7 +4247,7 @@
         <v>192</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>108</v>
@@ -4238,21 +4262,21 @@
         <v>106</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M64" s="8"/>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" ht="27.6">
       <c r="A65" s="1" t="s">
         <v>193</v>
       </c>
@@ -4260,7 +4284,7 @@
         <v>194</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>108</v>
@@ -4275,17 +4299,17 @@
         <v>106</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M65" s="8"/>
     </row>
@@ -4312,17 +4336,17 @@
         <v>106</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
         <v>31</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M66" s="8"/>
     </row>
@@ -4349,17 +4373,17 @@
         <v>106</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
         <v>31</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M67" s="8"/>
     </row>
@@ -4371,73 +4395,73 @@
         <v>200</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
         <v>31</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M68" s="8"/>
     </row>
     <row r="69" spans="1:13" ht="27.6">
       <c r="A69" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M69" s="8"/>
     </row>
-    <row r="70" spans="1:13" ht="27.6">
+    <row r="70" spans="1:13">
       <c r="A70" s="1" t="s">
         <v>204</v>
       </c>
@@ -4445,36 +4469,36 @@
         <v>205</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M70" s="8"/>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" ht="27.6">
       <c r="A71" s="1" t="s">
         <v>206</v>
       </c>
@@ -4482,36 +4506,36 @@
         <v>207</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M71" s="8"/>
     </row>
-    <row r="72" spans="1:13" ht="27.6">
+    <row r="72" spans="1:13">
       <c r="A72" s="1" t="s">
         <v>208</v>
       </c>
@@ -4519,29 +4543,29 @@
         <v>209</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>32</v>
@@ -4556,29 +4580,29 @@
         <v>211</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>32</v>
@@ -4593,29 +4617,29 @@
         <v>213</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>32</v>
@@ -4630,29 +4654,29 @@
         <v>215</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>32</v>
@@ -4667,36 +4691,36 @@
         <v>217</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M76" s="8"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" ht="27.6">
       <c r="A77" s="1" t="s">
         <v>218</v>
       </c>
@@ -4704,32 +4728,32 @@
         <v>219</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M77" s="8"/>
     </row>
@@ -4744,33 +4768,33 @@
         <v>80</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
         <v>31</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M78" s="8"/>
     </row>
-    <row r="79" spans="1:13" ht="27.6">
+    <row r="79" spans="1:13">
       <c r="A79" s="1" t="s">
         <v>222</v>
       </c>
@@ -4778,66 +4802,66 @@
         <v>223</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>201</v>
+        <v>41</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
         <v>31</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M79" s="8"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>41</v>
+        <v>222</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>32</v>
@@ -4852,29 +4876,29 @@
         <v>228</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>32</v>
@@ -4889,36 +4913,36 @@
         <v>230</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M82" s="8"/>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" ht="27.6">
       <c r="A83" s="1" t="s">
         <v>231</v>
       </c>
@@ -4926,29 +4950,29 @@
         <v>232</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>32</v>
@@ -4963,36 +4987,36 @@
         <v>234</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M84" s="8"/>
     </row>
-    <row r="85" spans="1:13" ht="27.6">
+    <row r="85" spans="1:13">
       <c r="A85" s="1" t="s">
         <v>235</v>
       </c>
@@ -5000,29 +5024,29 @@
         <v>236</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>32</v>
@@ -5037,29 +5061,29 @@
         <v>238</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>32</v>
@@ -5074,29 +5098,29 @@
         <v>240</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>224</v>
+        <v>41</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>32</v>
@@ -5105,35 +5129,35 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J88" s="1"/>
       <c r="K88" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>32</v>
@@ -5142,35 +5166,35 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>41</v>
+        <v>239</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J89" s="1"/>
       <c r="K89" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>32</v>
@@ -5185,29 +5209,29 @@
         <v>247</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>32</v>
@@ -5222,29 +5246,29 @@
         <v>249</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>32</v>
@@ -5259,36 +5283,36 @@
         <v>251</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M92" s="8"/>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" ht="27.6">
       <c r="A93" s="1" t="s">
         <v>252</v>
       </c>
@@ -5296,29 +5320,29 @@
         <v>253</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J93" s="1"/>
       <c r="K93" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L93" s="1" t="s">
         <v>32</v>
@@ -5333,29 +5357,29 @@
         <v>255</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J94" s="1"/>
       <c r="K94" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>32</v>
@@ -5370,29 +5394,29 @@
         <v>257</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>243</v>
+        <v>41</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J95" s="1"/>
       <c r="K95" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>32</v>
@@ -5401,72 +5425,72 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L96" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M96" s="8"/>
     </row>
-    <row r="97" spans="1:13" ht="27.6">
+    <row r="97" spans="1:13">
       <c r="A97" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>41</v>
+        <v>256</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J97" s="1"/>
       <c r="K97" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>32</v>
@@ -5481,36 +5505,36 @@
         <v>264</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M98" s="8"/>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" ht="27.6">
       <c r="A99" s="1" t="s">
         <v>265</v>
       </c>
@@ -5518,32 +5542,32 @@
         <v>266</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M99" s="8"/>
     </row>
@@ -5555,29 +5579,29 @@
         <v>268</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J100" s="1"/>
       <c r="K100" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>32</v>
@@ -5586,109 +5610,109 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J101" s="1"/>
       <c r="K101" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M101" s="8"/>
     </row>
-    <row r="102" spans="1:13" ht="27.6">
+    <row r="102" spans="1:13">
       <c r="A102" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J102" s="1"/>
       <c r="K102" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M102" s="8"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>41</v>
+        <v>267</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J103" s="1"/>
       <c r="K103" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L103" s="1" t="s">
         <v>32</v>
@@ -5697,35 +5721,35 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>32</v>
@@ -5740,29 +5764,29 @@
         <v>280</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>32</v>
@@ -5777,36 +5801,36 @@
         <v>282</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M106" s="8"/>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" ht="27.6">
       <c r="A107" s="1" t="s">
         <v>283</v>
       </c>
@@ -5814,29 +5838,29 @@
         <v>284</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J107" s="1"/>
       <c r="K107" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L107" s="1" t="s">
         <v>32</v>
@@ -5845,35 +5869,35 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J108" s="1"/>
       <c r="K108" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L108" s="1" t="s">
         <v>32</v>
@@ -5882,72 +5906,72 @@
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J109" s="1"/>
       <c r="K109" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L109" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M109" s="8"/>
     </row>
-    <row r="110" spans="1:13" ht="27.6">
+    <row r="110" spans="1:13">
       <c r="A110" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J110" s="1"/>
       <c r="K110" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L110" s="1" t="s">
         <v>32</v>
@@ -5962,66 +5986,66 @@
         <v>293</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>273</v>
+        <v>41</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J111" s="1"/>
       <c r="K111" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M111" s="8"/>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" ht="27.6">
       <c r="A112" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J112" s="1"/>
       <c r="K112" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>32</v>
@@ -6030,79 +6054,79 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J113" s="1"/>
       <c r="K113" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L113" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M113" s="8"/>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" ht="27.6">
       <c r="A114" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>41</v>
+        <v>292</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J114" s="1"/>
       <c r="K114" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M114" s="8"/>
     </row>
-    <row r="115" spans="1:13" ht="27.6">
+    <row r="115" spans="1:13">
       <c r="A115" s="1" t="s">
         <v>302</v>
       </c>
@@ -6110,29 +6134,29 @@
         <v>303</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J115" s="1"/>
       <c r="K115" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>32</v>
@@ -6147,36 +6171,36 @@
         <v>305</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J116" s="1"/>
       <c r="K116" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L116" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M116" s="8"/>
     </row>
-    <row r="117" spans="1:13" ht="27.6">
+    <row r="117" spans="1:13">
       <c r="A117" s="1" t="s">
         <v>306</v>
       </c>
@@ -6184,36 +6208,36 @@
         <v>307</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J117" s="1"/>
       <c r="K117" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M117" s="8"/>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" ht="27.6">
       <c r="A118" s="1" t="s">
         <v>308</v>
       </c>
@@ -6221,29 +6245,29 @@
         <v>309</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J118" s="1"/>
       <c r="K118" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>32</v>
@@ -6252,35 +6276,35 @@
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>298</v>
+        <v>41</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J119" s="1"/>
       <c r="K119" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L119" s="1" t="s">
         <v>32</v>
@@ -6289,72 +6313,72 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J120" s="1"/>
       <c r="K120" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M120" s="8"/>
     </row>
-    <row r="121" spans="1:13" ht="27.6">
+    <row r="121" spans="1:13">
       <c r="A121" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J121" s="1"/>
       <c r="K121" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L121" s="1" t="s">
         <v>32</v>
@@ -6363,35 +6387,35 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>41</v>
+        <v>311</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J122" s="1"/>
       <c r="K122" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L122" s="1" t="s">
         <v>32</v>
@@ -6406,29 +6430,29 @@
         <v>321</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J123" s="1"/>
       <c r="K123" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L123" s="1" t="s">
         <v>32</v>
@@ -6443,147 +6467,147 @@
         <v>323</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>317</v>
+        <v>56</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J124" s="1"/>
       <c r="K124" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L124" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M124" s="8"/>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" ht="27.6">
       <c r="A125" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J125" s="1"/>
       <c r="K125" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L125" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M125" s="8"/>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" ht="27.6">
       <c r="A126" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J126" s="1"/>
       <c r="K126" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M126" s="8"/>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" ht="27.6">
       <c r="A127" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>56</v>
+        <v>322</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J127" s="1"/>
       <c r="K127" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L127" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M127" s="8"/>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" ht="27.6">
       <c r="A128" s="1" t="s">
         <v>331</v>
       </c>
@@ -6591,29 +6615,29 @@
         <v>332</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J128" s="1"/>
       <c r="K128" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L128" s="1" t="s">
         <v>32</v>
@@ -6628,36 +6652,36 @@
         <v>334</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J129" s="1"/>
       <c r="K129" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L129" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M129" s="8"/>
     </row>
-    <row r="130" spans="1:13" ht="27.6">
+    <row r="130" spans="1:13">
       <c r="A130" s="1" t="s">
         <v>335</v>
       </c>
@@ -6665,140 +6689,140 @@
         <v>336</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>328</v>
+        <v>56</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J130" s="1"/>
       <c r="K130" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L130" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M130" s="8"/>
     </row>
-    <row r="131" spans="1:13" ht="27.6">
+    <row r="131" spans="1:13">
       <c r="A131" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J131" s="1"/>
       <c r="K131" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L131" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M131" s="8"/>
     </row>
-    <row r="132" spans="1:13" ht="27.6">
+    <row r="132" spans="1:13">
       <c r="A132" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J132" s="1"/>
       <c r="K132" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L132" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M132" s="8"/>
     </row>
-    <row r="133" spans="1:13" ht="27.6">
+    <row r="133" spans="1:13">
       <c r="A133" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J133" s="1"/>
       <c r="K133" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L133" s="1" t="s">
         <v>32</v>
@@ -6807,42 +6831,42 @@
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>56</v>
+        <v>335</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J134" s="1"/>
       <c r="K134" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L134" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M134" s="8"/>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" ht="27.6">
       <c r="A135" s="1" t="s">
         <v>346</v>
       </c>
@@ -6850,29 +6874,29 @@
         <v>347</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L135" s="1" t="s">
         <v>32</v>
@@ -6887,29 +6911,29 @@
         <v>349</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J136" s="1"/>
       <c r="K136" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>32</v>
@@ -6924,140 +6948,140 @@
         <v>351</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>343</v>
+        <v>56</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J137" s="1"/>
       <c r="K137" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L137" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M137" s="8"/>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" ht="27.6">
       <c r="A138" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J138" s="1"/>
       <c r="K138" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M138" s="8"/>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" ht="27.6">
       <c r="A139" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J139" s="1"/>
       <c r="K139" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M139" s="8"/>
     </row>
-    <row r="140" spans="1:13" ht="27.6">
+    <row r="140" spans="1:13">
       <c r="A140" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J140" s="1"/>
       <c r="K140" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>32</v>
@@ -7066,79 +7090,79 @@
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J141" s="1"/>
       <c r="K141" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L141" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M141" s="8"/>
     </row>
-    <row r="142" spans="1:13" ht="27.6">
+    <row r="142" spans="1:13">
       <c r="A142" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>56</v>
+        <v>350</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J142" s="1"/>
       <c r="K142" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L142" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M142" s="8"/>
     </row>
-    <row r="143" spans="1:13" ht="27.6">
+    <row r="143" spans="1:13">
       <c r="A143" s="1" t="s">
         <v>363</v>
       </c>
@@ -7146,36 +7170,36 @@
         <v>364</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J143" s="1"/>
       <c r="K143" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M143" s="8"/>
     </row>
-    <row r="144" spans="1:13" ht="27.6">
+    <row r="144" spans="1:13">
       <c r="A144" s="1" t="s">
         <v>365</v>
       </c>
@@ -7183,29 +7207,29 @@
         <v>366</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J144" s="1"/>
       <c r="K144" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L144" s="1" t="s">
         <v>32</v>
@@ -7220,29 +7244,29 @@
         <v>368</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J145" s="1"/>
       <c r="K145" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L145" s="1" t="s">
         <v>32</v>
@@ -7257,36 +7281,36 @@
         <v>370</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J146" s="1"/>
       <c r="K146" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L146" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M146" s="8"/>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" ht="27.6">
       <c r="A147" s="1" t="s">
         <v>371</v>
       </c>
@@ -7294,36 +7318,36 @@
         <v>372</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J147" s="1"/>
       <c r="K147" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M147" s="8"/>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" ht="27.6">
       <c r="A148" s="1" t="s">
         <v>373</v>
       </c>
@@ -7331,32 +7355,32 @@
         <v>374</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J148" s="1"/>
       <c r="K148" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M148" s="8"/>
     </row>
@@ -7368,221 +7392,221 @@
         <v>376</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>362</v>
+        <v>442</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>362</v>
+        <v>442</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>360</v>
+        <v>56</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="J149" s="1"/>
       <c r="K149" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L149" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M149" s="8"/>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" ht="27.6">
       <c r="A150" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J150" s="1"/>
       <c r="K150" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M150" s="8"/>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" ht="27.6">
       <c r="A151" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J151" s="1"/>
       <c r="K151" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L151" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M151" s="8"/>
     </row>
-    <row r="152" spans="1:13" ht="27.6">
+    <row r="152" spans="1:13">
       <c r="A152" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J152" s="1"/>
       <c r="K152" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M152" s="8"/>
     </row>
-    <row r="153" spans="1:13" ht="27.6">
+    <row r="153" spans="1:13">
       <c r="A153" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J153" s="1"/>
       <c r="K153" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M153" s="8"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>387</v>
+        <v>105</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>387</v>
+        <v>105</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="J154" s="1"/>
       <c r="K154" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M154" s="8"/>
     </row>
-    <row r="155" spans="1:13" ht="27.6">
+    <row r="155" spans="1:13">
       <c r="A155" s="1" t="s">
         <v>388</v>
       </c>
@@ -7590,32 +7614,32 @@
         <v>389</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J155" s="1"/>
       <c r="K155" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="M155" s="8"/>
     </row>
@@ -7627,36 +7651,36 @@
         <v>391</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J156" s="1"/>
       <c r="K156" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L156" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M156" s="8"/>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" ht="27.6">
       <c r="A157" s="1" t="s">
         <v>392</v>
       </c>
@@ -7664,29 +7688,29 @@
         <v>393</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J157" s="1"/>
       <c r="K157" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L157" s="1" t="s">
         <v>32</v>
@@ -7701,36 +7725,36 @@
         <v>395</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J158" s="1"/>
       <c r="K158" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L158" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M158" s="8"/>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" ht="27.6">
       <c r="A159" s="1" t="s">
         <v>396</v>
       </c>
@@ -7738,103 +7762,103 @@
         <v>397</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M159" s="8"/>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" ht="27.6">
       <c r="A160" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>385</v>
+        <v>56</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J160" s="1"/>
       <c r="K160" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M160" s="8"/>
     </row>
-    <row r="161" spans="1:13" ht="27.6">
+    <row r="161" spans="1:13">
       <c r="A161" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J161" s="1"/>
       <c r="K161" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L161" s="1" t="s">
         <v>32</v>
@@ -7843,35 +7867,35 @@
     </row>
     <row r="162" spans="1:13" ht="27.6">
       <c r="A162" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J162" s="1"/>
       <c r="K162" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L162" s="1" t="s">
         <v>32</v>
@@ -7880,35 +7904,35 @@
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J163" s="1"/>
       <c r="K163" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L163" s="1" t="s">
         <v>32</v>
@@ -7917,109 +7941,109 @@
     </row>
     <row r="164" spans="1:13" ht="27.6">
       <c r="A164" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J164" s="1"/>
       <c r="K164" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M164" s="8"/>
     </row>
     <row r="165" spans="1:13" ht="27.6">
       <c r="A165" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J165" s="1"/>
       <c r="K165" s="1" t="s">
         <v>31</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M165" s="8"/>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" ht="27.6">
       <c r="A166" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>408</v>
+        <v>101</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>408</v>
+        <v>101</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J166" s="1"/>
       <c r="K166" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L166" s="1" t="s">
         <v>32</v>
@@ -8028,276 +8052,205 @@
     </row>
     <row r="167" spans="1:13" ht="27.6">
       <c r="A167" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>416</v>
+        <v>101</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>416</v>
+        <v>101</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J167" s="1"/>
       <c r="K167" s="1" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="M167" s="8"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>408</v>
+        <v>105</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>408</v>
+        <v>105</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J168" s="1"/>
       <c r="K168" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L168" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M168" s="8"/>
     </row>
-    <row r="169" spans="1:13" ht="27.6">
-      <c r="A169" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>56</v>
+    <row r="169" spans="1:13">
+      <c r="A169" t="s">
+        <v>436</v>
+      </c>
+      <c r="B169" t="s">
+        <v>439</v>
+      </c>
+      <c r="C169" t="s">
+        <v>124</v>
+      </c>
+      <c r="D169" t="s">
+        <v>136</v>
+      </c>
+      <c r="E169" t="s">
+        <v>97</v>
+      </c>
+      <c r="F169" t="s">
+        <v>136</v>
+      </c>
+      <c r="G169" t="s">
+        <v>112</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J169" s="1"/>
       <c r="K169" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M169" s="8"/>
-    </row>
-    <row r="170" spans="1:13" ht="27.6">
-      <c r="A170" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C170" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13">
+      <c r="A170" t="s">
+        <v>437</v>
+      </c>
+      <c r="B170" t="s">
+        <v>440</v>
+      </c>
+      <c r="C170" t="s">
         <v>80</v>
       </c>
-      <c r="D170" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E170" s="1" t="s">
+      <c r="D170" t="s">
+        <v>337</v>
+      </c>
+      <c r="E170" t="s">
         <v>58</v>
       </c>
-      <c r="F170" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>56</v>
+      <c r="F170" t="s">
+        <v>337</v>
+      </c>
+      <c r="G170" t="s">
+        <v>335</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J170" s="1"/>
       <c r="K170" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M170" s="8"/>
-    </row>
-    <row r="171" spans="1:13" ht="27.6">
-      <c r="A171" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>98</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13">
+      <c r="A171" t="s">
+        <v>438</v>
+      </c>
+      <c r="B171" t="s">
+        <v>441</v>
+      </c>
+      <c r="C171" t="s">
+        <v>124</v>
+      </c>
+      <c r="D171" t="s">
+        <v>377</v>
+      </c>
+      <c r="E171" t="s">
+        <v>58</v>
+      </c>
+      <c r="F171" t="s">
+        <v>377</v>
+      </c>
+      <c r="G171" t="s">
+        <v>375</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J171" s="1"/>
       <c r="K171" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L171" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M171" s="8"/>
-    </row>
-    <row r="172" spans="1:13" ht="27.6">
-      <c r="A172" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H172" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I172" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J172" s="1"/>
-      <c r="K172" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L172" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M172" s="8"/>
-    </row>
-    <row r="173" spans="1:13">
-      <c r="A173" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H173" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I173" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J173" s="1"/>
-      <c r="K173" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L173" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M173" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K173">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="K2:K171">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>K2="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L173">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="L2:L171">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>L2&lt;&gt;"OK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>L2="OK"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A171">
+    <cfRule type="duplicateValues" dxfId="1" priority="163"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B171">
+    <cfRule type="duplicateValues" dxfId="0" priority="165"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -8319,79 +8272,79 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="B2" s="1">
         <v>181</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.6">
       <c r="A3" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B3" s="1">
         <v>181</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="27.6">
       <c r="A4" s="1" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="27.6">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="41.4">
       <c r="A5" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="B5" s="1">
         <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.6">
       <c r="A6" s="1" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B6" s="1">
         <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.6">
       <c r="A7" s="1" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B7" s="1">
         <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8405,315 +8358,315 @@
         <v>16</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27.6">
       <c r="A13" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27.6">
       <c r="A14" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.6">
       <c r="A16" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="27.6">
       <c r="A19" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="27.6">
       <c r="A24" s="1" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="27.6">
       <c r="A28" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="27.6">
       <c r="A29" s="1" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
